--- a/artfynd/A 21084-2025 artfynd.xlsx
+++ b/artfynd/A 21084-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124874578</v>
+        <v>124874764</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,23 +717,23 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 21081,, Sm</t>
+          <t>A 21084, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574826</v>
+        <v>574785</v>
       </c>
       <c r="R2" t="n">
-        <v>6415085</v>
+        <v>6415103</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124874764</v>
+        <v>124874578</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,23 +831,23 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 21084, Rispetorp, Sm</t>
+          <t>A 21081,, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574785</v>
+        <v>574826</v>
       </c>
       <c r="R3" t="n">
-        <v>6415103</v>
+        <v>6415085</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 21084-2025 artfynd.xlsx
+++ b/artfynd/A 21084-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124874764</v>
+        <v>124874679</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>105117</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 21084, Rispetorp, Sm</t>
+          <t>A 21081, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574785</v>
+        <v>574788</v>
       </c>
       <c r="R2" t="n">
-        <v>6415103</v>
+        <v>6415121</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -903,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124874679</v>
+        <v>124874764</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,46 +912,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 21081, Rispetorp, Sm</t>
+          <t>A 21084, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574788</v>
+        <v>574785</v>
       </c>
       <c r="R4" t="n">
-        <v>6415121</v>
+        <v>6415103</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21084-2025 artfynd.xlsx
+++ b/artfynd/A 21084-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124874679</v>
+        <v>124874578</v>
       </c>
       <c r="B2" t="n">
-        <v>105117</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 21081, Rispetorp, Sm</t>
+          <t>A 21081,, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574788</v>
+        <v>574826</v>
       </c>
       <c r="R2" t="n">
-        <v>6415121</v>
+        <v>6415085</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124874578</v>
+        <v>124874679</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,53 +801,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 21081,, Sm</t>
+          <t>A 21081, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574826</v>
+        <v>574788</v>
       </c>
       <c r="R3" t="n">
-        <v>6415085</v>
+        <v>6415121</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21084-2025 artfynd.xlsx
+++ b/artfynd/A 21084-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124874679</v>
+        <v>124874764</v>
       </c>
       <c r="B3" t="n">
-        <v>105117</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,46 +801,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 21081, Rispetorp, Sm</t>
+          <t>A 21084, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574788</v>
+        <v>574785</v>
       </c>
       <c r="R3" t="n">
-        <v>6415121</v>
+        <v>6415103</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124874764</v>
+        <v>124874679</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>105117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,50 +915,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 21084, Rispetorp, Sm</t>
+          <t>A 21081, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574785</v>
+        <v>574788</v>
       </c>
       <c r="R4" t="n">
-        <v>6415103</v>
+        <v>6415121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,6 +995,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21084-2025 artfynd.xlsx
+++ b/artfynd/A 21084-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124874764</v>
+        <v>124874679</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>105117</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,50 +801,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 21084, Rispetorp, Sm</t>
+          <t>A 21081, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574785</v>
+        <v>574788</v>
       </c>
       <c r="R3" t="n">
-        <v>6415103</v>
+        <v>6415121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124874679</v>
+        <v>124874764</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,46 +912,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 21081, Rispetorp, Sm</t>
+          <t>A 21084, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574788</v>
+        <v>574785</v>
       </c>
       <c r="R4" t="n">
-        <v>6415121</v>
+        <v>6415103</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21084-2025 artfynd.xlsx
+++ b/artfynd/A 21084-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124874578</v>
+        <v>124874764</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,23 +717,23 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 21081,, Sm</t>
+          <t>A 21084, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574826</v>
+        <v>574785</v>
       </c>
       <c r="R2" t="n">
-        <v>6415085</v>
+        <v>6415103</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124874764</v>
+        <v>124874679</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>105117</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,50 +801,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 21084, Rispetorp, Sm</t>
+          <t>A 21081, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574785</v>
+        <v>574788</v>
       </c>
       <c r="R3" t="n">
-        <v>6415103</v>
+        <v>6415121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124874679</v>
+        <v>124874578</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,49 +912,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 21081, Rispetorp, Sm</t>
+          <t>A 21081,, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574788</v>
+        <v>574826</v>
       </c>
       <c r="R4" t="n">
-        <v>6415121</v>
+        <v>6415085</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21084-2025 artfynd.xlsx
+++ b/artfynd/A 21084-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124874679</v>
+        <v>124874578</v>
       </c>
       <c r="B3" t="n">
-        <v>105117</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,49 +801,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 21081, Rispetorp, Sm</t>
+          <t>A 21081,, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574788</v>
+        <v>574826</v>
       </c>
       <c r="R3" t="n">
-        <v>6415121</v>
+        <v>6415085</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124874578</v>
+        <v>124874679</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,53 +915,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 21081,, Sm</t>
+          <t>A 21081, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574826</v>
+        <v>574788</v>
       </c>
       <c r="R4" t="n">
-        <v>6415085</v>
+        <v>6415121</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,6 +995,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21084-2025 artfynd.xlsx
+++ b/artfynd/A 21084-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124874764</v>
+        <v>124874679</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>105117</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 21084, Rispetorp, Sm</t>
+          <t>A 21081, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574785</v>
+        <v>574788</v>
       </c>
       <c r="R2" t="n">
-        <v>6415103</v>
+        <v>6415121</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124874578</v>
+        <v>124874764</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,23 +828,23 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 21081,, Sm</t>
+          <t>A 21084, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574826</v>
+        <v>574785</v>
       </c>
       <c r="R3" t="n">
-        <v>6415085</v>
+        <v>6415103</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -903,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124874679</v>
+        <v>124874578</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,49 +912,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 21081, Rispetorp, Sm</t>
+          <t>A 21081,, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574788</v>
+        <v>574826</v>
       </c>
       <c r="R4" t="n">
-        <v>6415121</v>
+        <v>6415085</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21084-2025 artfynd.xlsx
+++ b/artfynd/A 21084-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124874679</v>
+        <v>124874578</v>
       </c>
       <c r="B2" t="n">
-        <v>105117</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 21081, Rispetorp, Sm</t>
+          <t>A 21081,, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574788</v>
+        <v>574826</v>
       </c>
       <c r="R2" t="n">
-        <v>6415121</v>
+        <v>6415085</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124874764</v>
+        <v>124874679</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>105117</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,50 +801,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 21084, Rispetorp, Sm</t>
+          <t>A 21081, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574785</v>
+        <v>574788</v>
       </c>
       <c r="R3" t="n">
-        <v>6415103</v>
+        <v>6415121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124874578</v>
+        <v>124874764</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -942,23 +942,23 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 21081,, Sm</t>
+          <t>A 21084, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574826</v>
+        <v>574785</v>
       </c>
       <c r="R4" t="n">
-        <v>6415085</v>
+        <v>6415103</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 21084-2025 artfynd.xlsx
+++ b/artfynd/A 21084-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124874578</v>
+        <v>124874679</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>105117</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 21081,, Sm</t>
+          <t>A 21081, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574826</v>
+        <v>574788</v>
       </c>
       <c r="R2" t="n">
-        <v>6415085</v>
+        <v>6415121</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124874679</v>
+        <v>124874764</v>
       </c>
       <c r="B3" t="n">
-        <v>105117</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,46 +798,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 21081, Rispetorp, Sm</t>
+          <t>A 21084, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574788</v>
+        <v>574785</v>
       </c>
       <c r="R3" t="n">
-        <v>6415121</v>
+        <v>6415103</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124874764</v>
+        <v>124874578</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -942,23 +942,23 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 21084, Rispetorp, Sm</t>
+          <t>A 21081,, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574785</v>
+        <v>574826</v>
       </c>
       <c r="R4" t="n">
-        <v>6415103</v>
+        <v>6415085</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 21084-2025 artfynd.xlsx
+++ b/artfynd/A 21084-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124874679</v>
+        <v>124874578</v>
       </c>
       <c r="B2" t="n">
-        <v>105117</v>
+        <v>57793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 21081, Rispetorp, Sm</t>
+          <t>A 21081,, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574788</v>
+        <v>574826</v>
       </c>
       <c r="R2" t="n">
-        <v>6415121</v>
+        <v>6415085</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124874764</v>
+        <v>124874679</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>105293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,50 +801,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 21084, Rispetorp, Sm</t>
+          <t>A 21081, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574785</v>
+        <v>574788</v>
       </c>
       <c r="R3" t="n">
-        <v>6415103</v>
+        <v>6415121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124874578</v>
+        <v>124874764</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -942,23 +942,23 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 21081,, Sm</t>
+          <t>A 21084, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574826</v>
+        <v>574785</v>
       </c>
       <c r="R4" t="n">
-        <v>6415085</v>
+        <v>6415103</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 21084-2025 artfynd.xlsx
+++ b/artfynd/A 21084-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124874578</v>
+        <v>124874764</v>
       </c>
       <c r="B2" t="n">
-        <v>57793</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,23 +717,23 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 21081,, Sm</t>
+          <t>A 21084, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574826</v>
+        <v>574785</v>
       </c>
       <c r="R2" t="n">
-        <v>6415085</v>
+        <v>6415103</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124874764</v>
+        <v>124874578</v>
       </c>
       <c r="B4" t="n">
-        <v>57632</v>
+        <v>57793</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -942,23 +942,23 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 21084, Rispetorp, Sm</t>
+          <t>A 21081,, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574785</v>
+        <v>574826</v>
       </c>
       <c r="R4" t="n">
-        <v>6415103</v>
+        <v>6415085</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 21084-2025 artfynd.xlsx
+++ b/artfynd/A 21084-2025 artfynd.xlsx
@@ -675,62 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124874764</v>
+        <v>124874679</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 21084, Rispetorp, Sm</t>
+          <t>A 21081, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574785</v>
+        <v>574788</v>
       </c>
       <c r="R2" t="n">
-        <v>6415103</v>
+        <v>6415121</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,58 +781,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124874679</v>
+        <v>124874764</v>
       </c>
       <c r="B3" t="n">
-        <v>105293</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 21081, Rispetorp, Sm</t>
+          <t>A 21084, Rispetorp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574788</v>
+        <v>574785</v>
       </c>
       <c r="R3" t="n">
-        <v>6415121</v>
+        <v>6415103</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +872,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,11 +894,6 @@
       </c>
       <c r="B4" t="n">
         <v>57793</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
